--- a/data/fmsForecastOutput/File1/RPT_RPT4025233122954TF_fmsForecastOutput.xlsx
+++ b/data/fmsForecastOutput/File1/RPT_RPT4025233122954TF_fmsForecastOutput.xlsx
@@ -1875,19 +1875,19 @@
         </is>
       </c>
       <c r="C8" s="148" t="n">
-        <v>173.8198424841217</v>
+        <v>173.8198424841216</v>
       </c>
       <c r="D8" s="149" t="n">
-        <v>209.4488727090951</v>
+        <v>209.448872709095</v>
       </c>
       <c r="E8" s="149" t="n">
         <v>280.9281489347428</v>
       </c>
       <c r="F8" s="149" t="n">
-        <v>276.6502868378217</v>
+        <v>276.6502868378216</v>
       </c>
       <c r="G8" s="150" t="n">
-        <v>296.4313519362281</v>
+        <v>296.431351936228</v>
       </c>
       <c r="H8" s="148" t="n">
         <v>162.6288776297843</v>
@@ -1899,25 +1899,25 @@
         <v>150.2906984341075</v>
       </c>
       <c r="K8" s="149" t="n">
-        <v>131.8944711841467</v>
+        <v>131.8944711841466</v>
       </c>
       <c r="L8" s="150" t="n">
         <v>126.926431937151</v>
       </c>
       <c r="M8" s="151" t="n">
-        <v>28513.36897377078</v>
+        <v>28513.36897377076</v>
       </c>
       <c r="N8" s="152" t="n">
-        <v>27589.43109853494</v>
+        <v>27589.43109853493</v>
       </c>
       <c r="O8" s="152" t="n">
         <v>27615.53982529068</v>
       </c>
       <c r="P8" s="152" t="n">
-        <v>24878.69309532181</v>
+        <v>24878.69309532179</v>
       </c>
       <c r="Q8" s="153" t="n">
-        <v>24703.52033841372</v>
+        <v>24703.52033841371</v>
       </c>
       <c r="S8" s="21" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         </is>
       </c>
       <c r="T8" s="148" t="n">
-        <v>166.0699132013902</v>
+        <v>166.0699132013901</v>
       </c>
       <c r="U8" s="149" t="n">
         <v>200.1103879386258</v>
@@ -1934,16 +1934,16 @@
         <v>268.4026900650409</v>
       </c>
       <c r="W8" s="149" t="n">
-        <v>264.3155606730782</v>
+        <v>264.3155606730779</v>
       </c>
       <c r="X8" s="150" t="n">
         <v>283.2146674549949</v>
       </c>
       <c r="Y8" s="148" t="n">
-        <v>155.8252141268558</v>
+        <v>155.8252141268557</v>
       </c>
       <c r="Z8" s="149" t="n">
-        <v>148.5886171675649</v>
+        <v>148.5886171675648</v>
       </c>
       <c r="AA8" s="149" t="n">
         <v>146.6299793813728</v>
@@ -1952,22 +1952,22 @@
         <v>129.0238735459535</v>
       </c>
       <c r="AC8" s="150" t="n">
-        <v>124.4398981496567</v>
+        <v>124.4398981496566</v>
       </c>
       <c r="AD8" s="151" t="n">
-        <v>28513.36897377078</v>
+        <v>28513.36897377076</v>
       </c>
       <c r="AE8" s="152" t="n">
-        <v>27589.43109853494</v>
+        <v>27589.43109853493</v>
       </c>
       <c r="AF8" s="152" t="n">
         <v>27615.53982529068</v>
       </c>
       <c r="AG8" s="152" t="n">
-        <v>24878.69309532181</v>
+        <v>24878.69309532179</v>
       </c>
       <c r="AH8" s="153" t="n">
-        <v>24703.52033841372</v>
+        <v>24703.52033841371</v>
       </c>
       <c r="AQ8" s="28" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         </is>
       </c>
       <c r="C9" s="155" t="n">
-        <v>325.0005751247206</v>
+        <v>325.0005751247205</v>
       </c>
       <c r="D9" s="156" t="n">
         <v>413.5842697451503</v>
@@ -2031,40 +2031,40 @@
         <v>552.6331428004989</v>
       </c>
       <c r="F9" s="156" t="n">
-        <v>601.9135476813775</v>
+        <v>601.9135476813774</v>
       </c>
       <c r="G9" s="157" t="n">
-        <v>629.8372385861558</v>
+        <v>629.8372385861555</v>
       </c>
       <c r="H9" s="155" t="n">
-        <v>282.6116213425474</v>
+        <v>282.6116213425473</v>
       </c>
       <c r="I9" s="156" t="n">
-        <v>282.2815238382445</v>
+        <v>282.2815238382444</v>
       </c>
       <c r="J9" s="156" t="n">
         <v>294.1036792367452</v>
       </c>
       <c r="K9" s="156" t="n">
-        <v>304.9610529054245</v>
+        <v>304.9610529054244</v>
       </c>
       <c r="L9" s="157" t="n">
         <v>315.1345367056911</v>
       </c>
       <c r="M9" s="158" t="n">
-        <v>26067.50115945921</v>
+        <v>26067.5011594592</v>
       </c>
       <c r="N9" s="159" t="n">
-        <v>26846.67687501294</v>
+        <v>26846.67687501293</v>
       </c>
       <c r="O9" s="159" t="n">
         <v>28955.51136409166</v>
       </c>
       <c r="P9" s="159" t="n">
-        <v>31138.890965031</v>
+        <v>31138.89096503099</v>
       </c>
       <c r="Q9" s="160" t="n">
-        <v>33503.64851975265</v>
+        <v>33503.64851975264</v>
       </c>
       <c r="S9" s="32" t="inlineStr">
         <is>
@@ -2075,16 +2075,16 @@
         <v>326.4669752499568</v>
       </c>
       <c r="U9" s="156" t="n">
-        <v>415.4503588273536</v>
+        <v>415.4503588273535</v>
       </c>
       <c r="V9" s="156" t="n">
         <v>555.1266193412753</v>
       </c>
       <c r="W9" s="156" t="n">
-        <v>604.6293770344876</v>
+        <v>604.6293770344874</v>
       </c>
       <c r="X9" s="157" t="n">
-        <v>632.6790594204319</v>
+        <v>632.6790594204318</v>
       </c>
       <c r="Y9" s="155" t="n">
         <v>283.7197973971701</v>
@@ -2096,25 +2096,25 @@
         <v>294.8083992687835</v>
       </c>
       <c r="AB9" s="156" t="n">
-        <v>305.6566493308543</v>
+        <v>305.6566493308542</v>
       </c>
       <c r="AC9" s="157" t="n">
         <v>315.8443661912866</v>
       </c>
       <c r="AD9" s="158" t="n">
-        <v>26067.50115945921</v>
+        <v>26067.5011594592</v>
       </c>
       <c r="AE9" s="159" t="n">
-        <v>26846.67687501294</v>
+        <v>26846.67687501293</v>
       </c>
       <c r="AF9" s="159" t="n">
         <v>28955.51136409166</v>
       </c>
       <c r="AG9" s="159" t="n">
-        <v>31138.890965031</v>
+        <v>31138.89096503099</v>
       </c>
       <c r="AH9" s="160" t="n">
-        <v>33503.64851975265</v>
+        <v>33503.64851975264</v>
       </c>
       <c r="AJ9" s="39" t="n"/>
       <c r="AQ9" s="40" t="inlineStr">
@@ -2170,7 +2170,7 @@
         </is>
       </c>
       <c r="C10" s="161" t="n">
-        <v>223.4655704434068</v>
+        <v>223.4655704434067</v>
       </c>
       <c r="D10" s="162" t="n">
         <v>276.8366966654077</v>
@@ -2179,16 +2179,16 @@
         <v>375.3969558499179</v>
       </c>
       <c r="F10" s="162" t="n">
-        <v>395.4327373234509</v>
+        <v>395.4327373234507</v>
       </c>
       <c r="G10" s="163" t="n">
         <v>426.3307829181931</v>
       </c>
       <c r="H10" s="161" t="n">
-        <v>203.9905114907457</v>
+        <v>203.9905114907456</v>
       </c>
       <c r="I10" s="162" t="n">
-        <v>198.2121819693816</v>
+        <v>198.2121819693815</v>
       </c>
       <c r="J10" s="162" t="n">
         <v>200.4637430759367</v>
@@ -2200,16 +2200,16 @@
         <v>193.4152612515544</v>
       </c>
       <c r="M10" s="164" t="n">
-        <v>54580.87013322999</v>
+        <v>54580.87013322997</v>
       </c>
       <c r="N10" s="165" t="n">
-        <v>54436.10797354788</v>
+        <v>54436.10797354787</v>
       </c>
       <c r="O10" s="165" t="n">
         <v>56571.05118938234</v>
       </c>
       <c r="P10" s="165" t="n">
-        <v>56017.5840603528</v>
+        <v>56017.58406035278</v>
       </c>
       <c r="Q10" s="166" t="n">
         <v>58207.16885816635</v>
@@ -2220,46 +2220,46 @@
         </is>
       </c>
       <c r="T10" s="161" t="n">
-        <v>216.9848964891604</v>
+        <v>216.9848964891603</v>
       </c>
       <c r="U10" s="162" t="n">
-        <v>268.8312782850271</v>
+        <v>268.831278285027</v>
       </c>
       <c r="V10" s="162" t="n">
         <v>364.8599954259164</v>
       </c>
       <c r="W10" s="162" t="n">
-        <v>384.6681071195779</v>
+        <v>384.6681071195778</v>
       </c>
       <c r="X10" s="163" t="n">
-        <v>415.2297537793094</v>
+        <v>415.2297537793093</v>
       </c>
       <c r="Y10" s="161" t="n">
         <v>198.5765158701159</v>
       </c>
       <c r="Z10" s="162" t="n">
-        <v>194.0742920633844</v>
+        <v>194.0742920633843</v>
       </c>
       <c r="AA10" s="162" t="n">
         <v>197.419189962658</v>
       </c>
       <c r="AB10" s="162" t="n">
-        <v>190.0848441192867</v>
+        <v>190.0848441192866</v>
       </c>
       <c r="AC10" s="163" t="n">
         <v>191.0974729433113</v>
       </c>
       <c r="AD10" s="164" t="n">
-        <v>54580.87013322999</v>
+        <v>54580.87013322997</v>
       </c>
       <c r="AE10" s="165" t="n">
-        <v>54436.10797354788</v>
+        <v>54436.10797354787</v>
       </c>
       <c r="AF10" s="165" t="n">
         <v>56571.05118938234</v>
       </c>
       <c r="AG10" s="165" t="n">
-        <v>56017.5840603528</v>
+        <v>56017.58406035278</v>
       </c>
       <c r="AH10" s="166" t="n">
         <v>58207.16885816635</v>
@@ -2324,7 +2324,7 @@
         <v>746.0448097937978</v>
       </c>
       <c r="E11" s="156" t="n">
-        <v>946.3411488171488</v>
+        <v>946.3411488171491</v>
       </c>
       <c r="F11" s="156" t="n">
         <v>1104.353829764461</v>
@@ -2339,10 +2339,10 @@
         <v>662.052427863719</v>
       </c>
       <c r="J11" s="156" t="n">
-        <v>731.8905496159342</v>
+        <v>731.8905496159344</v>
       </c>
       <c r="K11" s="156" t="n">
-        <v>770.9033822804265</v>
+        <v>770.9033822804263</v>
       </c>
       <c r="L11" s="157" t="n">
         <v>759.903311773159</v>
@@ -2354,10 +2354,10 @@
         <v>70489.59896386128</v>
       </c>
       <c r="O11" s="159" t="n">
-        <v>82286.43761786017</v>
+        <v>82286.4376178602</v>
       </c>
       <c r="P11" s="159" t="n">
-        <v>91967.54477065787</v>
+        <v>91967.54477065784</v>
       </c>
       <c r="Q11" s="160" t="n">
         <v>96815.86147860867</v>
@@ -2374,10 +2374,10 @@
         <v>893.8881093632524</v>
       </c>
       <c r="V11" s="156" t="n">
-        <v>1133.877066395807</v>
+        <v>1133.877066395808</v>
       </c>
       <c r="W11" s="156" t="n">
-        <v>1323.203035524192</v>
+        <v>1323.203035524191</v>
       </c>
       <c r="X11" s="157" t="n">
         <v>1404.321619973049</v>
@@ -2389,10 +2389,10 @@
         <v>775.9393119356628</v>
       </c>
       <c r="AA11" s="156" t="n">
-        <v>839.2409214908024</v>
+        <v>839.2409214908027</v>
       </c>
       <c r="AB11" s="156" t="n">
-        <v>871.5246725950217</v>
+        <v>871.5246725950215</v>
       </c>
       <c r="AC11" s="157" t="n">
         <v>851.177651681036</v>
@@ -2404,10 +2404,10 @@
         <v>70489.59896386128</v>
       </c>
       <c r="AF11" s="159" t="n">
-        <v>82286.43761786017</v>
+        <v>82286.4376178602</v>
       </c>
       <c r="AG11" s="159" t="n">
-        <v>91967.54477065787</v>
+        <v>91967.54477065784</v>
       </c>
       <c r="AH11" s="160" t="n">
         <v>96815.86147860867</v>
@@ -2461,37 +2461,37 @@
         </is>
       </c>
       <c r="C12" s="161" t="n">
-        <v>335.3357078661716</v>
+        <v>335.3357078661715</v>
       </c>
       <c r="D12" s="162" t="n">
         <v>429.1201580598057</v>
       </c>
       <c r="E12" s="162" t="n">
-        <v>584.2970108514847</v>
+        <v>584.2970108514849</v>
       </c>
       <c r="F12" s="162" t="n">
-        <v>657.8908687818223</v>
+        <v>657.8908687818222</v>
       </c>
       <c r="G12" s="163" t="n">
-        <v>707.4349193391673</v>
+        <v>707.4349193391671</v>
       </c>
       <c r="H12" s="161" t="n">
-        <v>311.8071214912409</v>
+        <v>311.8071214912407</v>
       </c>
       <c r="I12" s="162" t="n">
-        <v>327.7970597571727</v>
+        <v>327.7970597571726</v>
       </c>
       <c r="J12" s="162" t="n">
-        <v>351.8667508660704</v>
+        <v>351.8667508660705</v>
       </c>
       <c r="K12" s="162" t="n">
-        <v>360.9112440096552</v>
+        <v>360.9112440096551</v>
       </c>
       <c r="L12" s="163" t="n">
-        <v>361.9077836579761</v>
+        <v>361.907783657976</v>
       </c>
       <c r="M12" s="164" t="n">
-        <v>114824.7968047025</v>
+        <v>114824.7968047024</v>
       </c>
       <c r="N12" s="165" t="n">
         <v>124925.7069374092</v>
@@ -2500,7 +2500,7 @@
         <v>138857.4888072425</v>
       </c>
       <c r="P12" s="165" t="n">
-        <v>147985.1288310107</v>
+        <v>147985.1288310106</v>
       </c>
       <c r="Q12" s="166" t="n">
         <v>155023.030336775</v>
@@ -2511,22 +2511,22 @@
         </is>
       </c>
       <c r="T12" s="161" t="n">
-        <v>344.3273634553058</v>
+        <v>344.3273634553057</v>
       </c>
       <c r="U12" s="162" t="n">
         <v>444.0239698499896</v>
       </c>
       <c r="V12" s="162" t="n">
-        <v>610.0421019959759</v>
+        <v>610.0421019959761</v>
       </c>
       <c r="W12" s="162" t="n">
         <v>687.888639620117</v>
       </c>
       <c r="X12" s="163" t="n">
-        <v>741.3042481458612</v>
+        <v>741.3042481458609</v>
       </c>
       <c r="Y12" s="161" t="n">
-        <v>319.566658644539</v>
+        <v>319.5666586445389</v>
       </c>
       <c r="Z12" s="162" t="n">
         <v>336.4229248591687</v>
@@ -2535,13 +2535,13 @@
         <v>361.0424130117514</v>
       </c>
       <c r="AB12" s="162" t="n">
-        <v>369.7569759834527</v>
+        <v>369.7569759834525</v>
       </c>
       <c r="AC12" s="163" t="n">
-        <v>370.5692395546512</v>
+        <v>370.5692395546511</v>
       </c>
       <c r="AD12" s="164" t="n">
-        <v>114824.7968047025</v>
+        <v>114824.7968047024</v>
       </c>
       <c r="AE12" s="165" t="n">
         <v>124925.7069374092</v>
@@ -2550,7 +2550,7 @@
         <v>138857.4888072425</v>
       </c>
       <c r="AG12" s="165" t="n">
-        <v>147985.1288310107</v>
+        <v>147985.1288310106</v>
       </c>
       <c r="AH12" s="166" t="n">
         <v>155023.030336775</v>
@@ -2746,25 +2746,25 @@
         </is>
       </c>
       <c r="C14" s="167" t="n">
-        <v>332.2984115506638</v>
+        <v>332.2984115506637</v>
       </c>
       <c r="D14" s="168" t="n">
         <v>424.4712217057527</v>
       </c>
       <c r="E14" s="168" t="n">
-        <v>576.3589261890754</v>
+        <v>576.3589261890755</v>
       </c>
       <c r="F14" s="168" t="n">
-        <v>648.2700529308528</v>
+        <v>648.2700529308527</v>
       </c>
       <c r="G14" s="169" t="n">
         <v>696.6115376608154</v>
       </c>
       <c r="H14" s="167" t="n">
-        <v>309.1794219356564</v>
+        <v>309.1794219356563</v>
       </c>
       <c r="I14" s="168" t="n">
-        <v>325.0773770877086</v>
+        <v>325.0773770877085</v>
       </c>
       <c r="J14" s="168" t="n">
         <v>348.9723525930174</v>
@@ -2776,7 +2776,7 @@
         <v>359.0538535480448</v>
       </c>
       <c r="M14" s="170" t="n">
-        <v>114824.7968047025</v>
+        <v>114824.7968047024</v>
       </c>
       <c r="N14" s="171" t="n">
         <v>124925.7069374092</v>
@@ -2785,7 +2785,7 @@
         <v>138857.4888072425</v>
       </c>
       <c r="P14" s="171" t="n">
-        <v>147985.1288310107</v>
+        <v>147985.1288310106</v>
       </c>
       <c r="Q14" s="172" t="n">
         <v>155023.030336775</v>
@@ -2796,13 +2796,13 @@
         </is>
       </c>
       <c r="T14" s="167" t="n">
-        <v>335.5104868164796</v>
+        <v>335.5104868164794</v>
       </c>
       <c r="U14" s="168" t="n">
         <v>430.36774696342</v>
       </c>
       <c r="V14" s="168" t="n">
-        <v>586.4306058728156</v>
+        <v>586.4306058728157</v>
       </c>
       <c r="W14" s="168" t="n">
         <v>659.2451962066948</v>
@@ -2811,7 +2811,7 @@
         <v>708.9838515505846</v>
       </c>
       <c r="Y14" s="167" t="n">
-        <v>311.9582288805414</v>
+        <v>311.9582288805413</v>
       </c>
       <c r="Z14" s="168" t="n">
         <v>328.5245476171249</v>
@@ -2820,13 +2820,13 @@
         <v>352.6393793873116</v>
       </c>
       <c r="AB14" s="168" t="n">
-        <v>361.3184492802508</v>
+        <v>361.3184492802507</v>
       </c>
       <c r="AC14" s="169" t="n">
         <v>362.3127240369342</v>
       </c>
       <c r="AD14" s="170" t="n">
-        <v>114824.7968047025</v>
+        <v>114824.7968047024</v>
       </c>
       <c r="AE14" s="171" t="n">
         <v>124925.7069374092</v>
@@ -2835,7 +2835,7 @@
         <v>138857.4888072425</v>
       </c>
       <c r="AG14" s="171" t="n">
-        <v>147985.1288310107</v>
+        <v>147985.1288310106</v>
       </c>
       <c r="AH14" s="172" t="n">
         <v>155023.030336775</v>
@@ -3709,7 +3709,7 @@
         <v>291.1205744848707</v>
       </c>
       <c r="E23" s="86" t="n">
-        <v>237.6488091302883</v>
+        <v>237.6488091302884</v>
       </c>
       <c r="F23" s="86" t="n">
         <v>224.9387183394504</v>
@@ -3721,7 +3721,7 @@
         <v>25.83840429144</v>
       </c>
       <c r="I23" s="86" t="n">
-        <v>89.98628178148</v>
+        <v>89.98628178147999</v>
       </c>
       <c r="J23" s="86" t="n">
         <v>156.98208016364</v>
@@ -3736,7 +3736,7 @@
         <v>368.2558507821897</v>
       </c>
       <c r="N23" s="86" t="n">
-        <v>381.1068562663506</v>
+        <v>381.1068562663507</v>
       </c>
       <c r="O23" s="86" t="n">
         <v>394.6308892939284</v>
@@ -3771,7 +3771,7 @@
         <v>25.83840429144</v>
       </c>
       <c r="Z23" s="86" t="n">
-        <v>89.98628178148</v>
+        <v>89.98628178147999</v>
       </c>
       <c r="AA23" s="86" t="n">
         <v>156.98208016364</v>
@@ -3960,7 +3960,7 @@
         <v>25.83840429144</v>
       </c>
       <c r="I25" s="92" t="n">
-        <v>89.98628178148</v>
+        <v>89.98628178147999</v>
       </c>
       <c r="J25" s="92" t="n">
         <v>156.98208016364</v>
@@ -3975,10 +3975,10 @@
         <v>371.3856377821897</v>
       </c>
       <c r="N25" s="92" t="n">
-        <v>384.2952962663506</v>
+        <v>384.2952962663507</v>
       </c>
       <c r="O25" s="92" t="n">
-        <v>397.9039822939283</v>
+        <v>397.9039822939284</v>
       </c>
       <c r="P25" s="92" t="n">
         <v>413.3701758442504</v>
@@ -4010,7 +4010,7 @@
         <v>25.83840429144</v>
       </c>
       <c r="Z25" s="92" t="n">
-        <v>89.98628178148</v>
+        <v>89.98628178147999</v>
       </c>
       <c r="AA25" s="92" t="n">
         <v>156.98208016364</v>
@@ -4408,22 +4408,22 @@
         </is>
       </c>
       <c r="C35" s="148" t="n">
-        <v>176.9719128457909</v>
+        <v>176.9719128457908</v>
       </c>
       <c r="D35" s="149" t="n">
         <v>218.7877020820015</v>
       </c>
       <c r="E35" s="149" t="n">
-        <v>295.7389391429956</v>
+        <v>295.7389391429955</v>
       </c>
       <c r="F35" s="149" t="n">
-        <v>295.0796240129791</v>
+        <v>295.079624012979</v>
       </c>
       <c r="G35" s="150" t="n">
-        <v>316.9561178112163</v>
+        <v>316.9561178112162</v>
       </c>
       <c r="H35" s="148" t="n">
-        <v>165.5780096609861</v>
+        <v>165.578009660986</v>
       </c>
       <c r="I35" s="149" t="n">
         <v>160.5283770874522</v>
@@ -4432,13 +4432,13 @@
         <v>158.2141621852477</v>
       </c>
       <c r="K35" s="149" t="n">
-        <v>140.6807540713814</v>
+        <v>140.6807540713813</v>
       </c>
       <c r="L35" s="150" t="n">
-        <v>135.7147577395382</v>
+        <v>135.7147577395381</v>
       </c>
       <c r="M35" s="151" t="n">
-        <v>29030.43390703218</v>
+        <v>29030.43390703216</v>
       </c>
       <c r="N35" s="152" t="n">
         <v>28819.57851442785</v>
@@ -4447,7 +4447,7 @@
         <v>29071.4564658657</v>
       </c>
       <c r="P35" s="152" t="n">
-        <v>26536.01226448546</v>
+        <v>26536.01226448544</v>
       </c>
       <c r="Q35" s="153" t="n">
         <v>26413.98034179092</v>
@@ -4461,13 +4461,13 @@
         <v>169.0814453940677</v>
       </c>
       <c r="U35" s="149" t="n">
-        <v>209.0328363840779</v>
+        <v>209.0328363840778</v>
       </c>
       <c r="V35" s="149" t="n">
         <v>282.553126569741</v>
       </c>
       <c r="W35" s="149" t="n">
-        <v>281.9232076557126</v>
+        <v>281.9232076557124</v>
       </c>
       <c r="X35" s="150" t="n">
         <v>302.8243163801429</v>
@@ -4482,13 +4482,13 @@
         <v>154.3604466595465</v>
       </c>
       <c r="AB35" s="149" t="n">
-        <v>137.6189286836234</v>
+        <v>137.6189286836233</v>
       </c>
       <c r="AC35" s="150" t="n">
-        <v>133.0560575347765</v>
+        <v>133.0560575347764</v>
       </c>
       <c r="AD35" s="151" t="n">
-        <v>29030.43390703218</v>
+        <v>29030.43390703216</v>
       </c>
       <c r="AE35" s="152" t="n">
         <v>28819.57851442785</v>
@@ -4497,7 +4497,7 @@
         <v>29071.4564658657</v>
       </c>
       <c r="AG35" s="152" t="n">
-        <v>26536.01226448546</v>
+        <v>26536.01226448544</v>
       </c>
       <c r="AH35" s="153" t="n">
         <v>26413.98034179092</v>
@@ -4519,16 +4519,16 @@
         <v>580.9695888307106</v>
       </c>
       <c r="F36" s="156" t="n">
-        <v>640.7480713681733</v>
+        <v>640.7480713681732</v>
       </c>
       <c r="G36" s="157" t="n">
-        <v>672.1270045287202</v>
+        <v>672.12700452872</v>
       </c>
       <c r="H36" s="155" t="n">
         <v>286.1132968432142</v>
       </c>
       <c r="I36" s="156" t="n">
-        <v>294.6615670797992</v>
+        <v>294.6615670797991</v>
       </c>
       <c r="J36" s="156" t="n">
         <v>309.1839420522298</v>
@@ -4537,10 +4537,10 @@
         <v>324.6366645912325</v>
       </c>
       <c r="L36" s="157" t="n">
-        <v>336.2939172269481</v>
+        <v>336.293917226948</v>
       </c>
       <c r="M36" s="158" t="n">
-        <v>26390.48833790594</v>
+        <v>26390.48833790593</v>
       </c>
       <c r="N36" s="159" t="n">
         <v>28024.09371790613</v>
@@ -4549,10 +4549,10 @@
         <v>30440.21472605048</v>
       </c>
       <c r="P36" s="159" t="n">
-        <v>33147.92366319876</v>
+        <v>33147.92366319875</v>
       </c>
       <c r="Q36" s="160" t="n">
-        <v>35753.21613392361</v>
+        <v>35753.2161339236</v>
       </c>
       <c r="S36" s="32" t="inlineStr">
         <is>
@@ -4569,13 +4569,13 @@
         <v>583.5909192006426</v>
       </c>
       <c r="W36" s="156" t="n">
-        <v>643.639121797049</v>
+        <v>643.6391217970489</v>
       </c>
       <c r="X36" s="157" t="n">
-        <v>675.1596364655632</v>
+        <v>675.159636465563</v>
       </c>
       <c r="Y36" s="155" t="n">
-        <v>287.2352036599425</v>
+        <v>287.2352036599424</v>
       </c>
       <c r="Z36" s="156" t="n">
         <v>295.5676931723218</v>
@@ -4587,10 +4587,10 @@
         <v>325.3771398135657</v>
       </c>
       <c r="AC36" s="157" t="n">
-        <v>337.0514074746674</v>
+        <v>337.0514074746673</v>
       </c>
       <c r="AD36" s="158" t="n">
-        <v>26390.48833790594</v>
+        <v>26390.48833790593</v>
       </c>
       <c r="AE36" s="159" t="n">
         <v>28024.09371790613</v>
@@ -4599,10 +4599,10 @@
         <v>30440.21472605048</v>
       </c>
       <c r="AG36" s="159" t="n">
-        <v>33147.92366319876</v>
+        <v>33147.92366319875</v>
       </c>
       <c r="AH36" s="160" t="n">
-        <v>35753.21613392361</v>
+        <v>35753.2161339236</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" thickTop="1">
@@ -4612,7 +4612,7 @@
         </is>
       </c>
       <c r="C37" s="161" t="n">
-        <v>226.9049206019297</v>
+        <v>226.9049206019296</v>
       </c>
       <c r="D37" s="162" t="n">
         <v>289.0804473893925</v>
@@ -4621,13 +4621,13 @@
         <v>394.9104662771338</v>
       </c>
       <c r="F37" s="162" t="n">
-        <v>421.3138169738658</v>
+        <v>421.3138169738656</v>
       </c>
       <c r="G37" s="163" t="n">
-        <v>455.3354864226845</v>
+        <v>455.3354864226844</v>
       </c>
       <c r="H37" s="161" t="n">
-        <v>207.1301217521419</v>
+        <v>207.1301217521418</v>
       </c>
       <c r="I37" s="162" t="n">
         <v>206.9785795450014</v>
@@ -4636,25 +4636,25 @@
         <v>210.8840495803798</v>
       </c>
       <c r="K37" s="162" t="n">
-        <v>205.2874330935731</v>
+        <v>205.287433093573</v>
       </c>
       <c r="L37" s="163" t="n">
         <v>206.5739458472233</v>
       </c>
       <c r="M37" s="164" t="n">
-        <v>55420.92224493811</v>
+        <v>55420.92224493809</v>
       </c>
       <c r="N37" s="165" t="n">
-        <v>56843.67223233398</v>
+        <v>56843.67223233397</v>
       </c>
       <c r="O37" s="165" t="n">
         <v>59511.67119191618</v>
       </c>
       <c r="P37" s="165" t="n">
-        <v>59683.93592768422</v>
+        <v>59683.93592768419</v>
       </c>
       <c r="Q37" s="166" t="n">
-        <v>62167.19647571453</v>
+        <v>62167.19647571452</v>
       </c>
       <c r="S37" s="42" t="inlineStr">
         <is>
@@ -4662,22 +4662,22 @@
         </is>
       </c>
       <c r="T37" s="161" t="n">
-        <v>220.324502839509</v>
+        <v>220.3245028395089</v>
       </c>
       <c r="U37" s="162" t="n">
-        <v>280.7209706479954</v>
+        <v>280.7209706479953</v>
       </c>
       <c r="V37" s="162" t="n">
         <v>383.8257840778201</v>
       </c>
       <c r="W37" s="162" t="n">
-        <v>409.8446415327942</v>
+        <v>409.844641532794</v>
       </c>
       <c r="X37" s="163" t="n">
-        <v>443.4792172878425</v>
+        <v>443.4792172878424</v>
       </c>
       <c r="Y37" s="161" t="n">
-        <v>201.6327995293018</v>
+        <v>201.6327995293017</v>
       </c>
       <c r="Z37" s="162" t="n">
         <v>202.6576817750087</v>
@@ -4692,19 +4692,19 @@
         <v>204.0984706785414</v>
       </c>
       <c r="AD37" s="164" t="n">
-        <v>55420.92224493811</v>
+        <v>55420.92224493809</v>
       </c>
       <c r="AE37" s="165" t="n">
-        <v>56843.67223233398</v>
+        <v>56843.67223233397</v>
       </c>
       <c r="AF37" s="165" t="n">
         <v>59511.67119191618</v>
       </c>
       <c r="AG37" s="165" t="n">
-        <v>59683.93592768422</v>
+        <v>59683.93592768419</v>
       </c>
       <c r="AH37" s="166" t="n">
-        <v>62167.19647571453</v>
+        <v>62167.19647571452</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" thickBot="1">
@@ -4720,7 +4720,7 @@
         <v>780.5008674312877</v>
       </c>
       <c r="E38" s="156" t="n">
-        <v>996.0862930602527</v>
+        <v>996.0862930602531</v>
       </c>
       <c r="F38" s="156" t="n">
         <v>1176.2339707586</v>
@@ -4735,10 +4735,10 @@
         <v>692.6292998076676</v>
       </c>
       <c r="J38" s="156" t="n">
-        <v>770.3629345548289</v>
+        <v>770.3629345548292</v>
       </c>
       <c r="K38" s="156" t="n">
-        <v>821.079912951755</v>
+        <v>821.0799129517547</v>
       </c>
       <c r="L38" s="157" t="n">
         <v>810.265685069118</v>
@@ -4750,10 +4750,10 @@
         <v>73745.15902253076</v>
       </c>
       <c r="O38" s="159" t="n">
-        <v>86611.88696946872</v>
+        <v>86611.88696946875</v>
       </c>
       <c r="P38" s="159" t="n">
-        <v>97953.52490386354</v>
+        <v>97953.52490386351</v>
       </c>
       <c r="Q38" s="160" t="n">
         <v>103232.3048355644</v>
@@ -4773,7 +4773,7 @@
         <v>1193.48017917634</v>
       </c>
       <c r="W38" s="156" t="n">
-        <v>1409.3276254825</v>
+        <v>1409.327625482499</v>
       </c>
       <c r="X38" s="157" t="n">
         <v>1497.392631188461</v>
@@ -4785,10 +4785,10 @@
         <v>811.7760462769139</v>
       </c>
       <c r="AA38" s="156" t="n">
-        <v>883.3562606012883</v>
+        <v>883.3562606012887</v>
       </c>
       <c r="AB38" s="156" t="n">
-        <v>928.2504380676347</v>
+        <v>928.2504380676344</v>
       </c>
       <c r="AC38" s="157" t="n">
         <v>907.5892055866394</v>
@@ -4800,10 +4800,10 @@
         <v>73745.15902253076</v>
       </c>
       <c r="AF38" s="159" t="n">
-        <v>86611.88696946872</v>
+        <v>86611.88696946875</v>
       </c>
       <c r="AG38" s="159" t="n">
-        <v>97953.52490386354</v>
+        <v>97953.52490386351</v>
       </c>
       <c r="AH38" s="160" t="n">
         <v>103232.3048355644</v>
@@ -4816,7 +4816,7 @@
         </is>
       </c>
       <c r="C39" s="161" t="n">
-        <v>341.732738498075</v>
+        <v>341.7327384980749</v>
       </c>
       <c r="D39" s="162" t="n">
         <v>448.5730061708549</v>
@@ -4825,25 +4825,25 @@
         <v>614.8718299752736</v>
       </c>
       <c r="F39" s="162" t="n">
-        <v>700.8018094673247</v>
+        <v>700.8018094673246</v>
       </c>
       <c r="G39" s="163" t="n">
-        <v>754.7870959217457</v>
+        <v>754.7870959217455</v>
       </c>
       <c r="H39" s="161" t="n">
-        <v>317.7553091152714</v>
+        <v>317.7553091152712</v>
       </c>
       <c r="I39" s="162" t="n">
-        <v>342.6567355261589</v>
+        <v>342.6567355261588</v>
       </c>
       <c r="J39" s="162" t="n">
-        <v>370.2790686832154</v>
+        <v>370.2790686832155</v>
       </c>
       <c r="K39" s="162" t="n">
-        <v>384.45168471087</v>
+        <v>384.4516847108699</v>
       </c>
       <c r="L39" s="163" t="n">
-        <v>386.1320915199492</v>
+        <v>386.1320915199491</v>
       </c>
       <c r="M39" s="164" t="n">
         <v>117015.2516988019</v>
@@ -4866,31 +4866,31 @@
         </is>
       </c>
       <c r="T39" s="161" t="n">
-        <v>350.8959233782626</v>
+        <v>350.8959233782625</v>
       </c>
       <c r="U39" s="162" t="n">
         <v>464.1524366230494</v>
       </c>
       <c r="V39" s="162" t="n">
-        <v>641.9640981383861</v>
+        <v>641.9640981383862</v>
       </c>
       <c r="W39" s="162" t="n">
         <v>732.7561853083956</v>
       </c>
       <c r="X39" s="163" t="n">
-        <v>790.9234692219261</v>
+        <v>790.9234692219259</v>
       </c>
       <c r="Y39" s="161" t="n">
-        <v>325.6628710559532</v>
+        <v>325.6628710559531</v>
       </c>
       <c r="Z39" s="162" t="n">
         <v>351.6736278043523</v>
       </c>
       <c r="AA39" s="162" t="n">
-        <v>379.9348705613183</v>
+        <v>379.9348705613184</v>
       </c>
       <c r="AB39" s="162" t="n">
-        <v>393.8743796705656</v>
+        <v>393.8743796705655</v>
       </c>
       <c r="AC39" s="163" t="n">
         <v>395.3733022150793</v>
@@ -5020,22 +5020,22 @@
         </is>
       </c>
       <c r="C41" s="179" t="n">
-        <v>338.6375012084547</v>
+        <v>338.6375012084546</v>
       </c>
       <c r="D41" s="180" t="n">
         <v>443.7133245253614</v>
       </c>
       <c r="E41" s="180" t="n">
-        <v>606.5183649528162</v>
+        <v>606.5183649528163</v>
       </c>
       <c r="F41" s="180" t="n">
         <v>690.5534757742371</v>
       </c>
       <c r="G41" s="181" t="n">
-        <v>743.2392508808379</v>
+        <v>743.2392508808377</v>
       </c>
       <c r="H41" s="179" t="n">
-        <v>315.0774822569446</v>
+        <v>315.0774822569445</v>
       </c>
       <c r="I41" s="180" t="n">
         <v>339.8137643723724</v>
@@ -5070,34 +5070,34 @@
         </is>
       </c>
       <c r="T41" s="185" t="n">
-        <v>341.9108516185077</v>
+        <v>341.9108516185076</v>
       </c>
       <c r="U41" s="186" t="n">
         <v>449.877150696458</v>
       </c>
       <c r="V41" s="186" t="n">
-        <v>617.1170707532129</v>
+        <v>617.1170707532131</v>
       </c>
       <c r="W41" s="186" t="n">
         <v>702.2444729165367</v>
       </c>
       <c r="X41" s="187" t="n">
-        <v>756.4397059550862</v>
+        <v>756.4397059550861</v>
       </c>
       <c r="Y41" s="185" t="n">
-        <v>317.9092991042337</v>
+        <v>317.9092991042336</v>
       </c>
       <c r="Z41" s="186" t="n">
         <v>343.4172018201849</v>
       </c>
       <c r="AA41" s="186" t="n">
-        <v>371.0921269462627</v>
+        <v>371.0921269462629</v>
       </c>
       <c r="AB41" s="186" t="n">
         <v>384.8854499506679</v>
       </c>
       <c r="AC41" s="187" t="n">
-        <v>386.5641365947679</v>
+        <v>386.5641365947678</v>
       </c>
       <c r="AD41" s="188" t="n">
         <v>117015.2516988019</v>
@@ -6334,10 +6334,10 @@
         </is>
       </c>
       <c r="C57" s="148" t="n">
-        <v>0.1287624819691243</v>
+        <v>0.1287624819691242</v>
       </c>
       <c r="D57" s="149" t="n">
-        <v>0.01961737841367162</v>
+        <v>0.01961737841367161</v>
       </c>
       <c r="E57" s="149" t="n">
         <v>0</v>
@@ -6349,10 +6349,10 @@
         <v>0</v>
       </c>
       <c r="H57" s="148" t="n">
-        <v>0.1204724249210899</v>
+        <v>0.1204724249210898</v>
       </c>
       <c r="I57" s="149" t="n">
-        <v>0.01439361485810032</v>
+        <v>0.01439361485810031</v>
       </c>
       <c r="J57" s="149" t="n">
         <v>0</v>
@@ -6364,10 +6364,10 @@
         <v>0</v>
       </c>
       <c r="M57" s="151" t="n">
-        <v>21.12216940191699</v>
+        <v>21.12216940191698</v>
       </c>
       <c r="N57" s="152" t="n">
-        <v>2.584078410532202</v>
+        <v>2.5840784105322</v>
       </c>
       <c r="O57" s="152" t="n">
         <v>0</v>
@@ -6384,10 +6384,10 @@
         </is>
       </c>
       <c r="T57" s="148" t="n">
-        <v>0.1230214795883353</v>
+        <v>0.1230214795883352</v>
       </c>
       <c r="U57" s="149" t="n">
-        <v>0.01874271822962257</v>
+        <v>0.01874271822962255</v>
       </c>
       <c r="V57" s="149" t="n">
         <v>0</v>
@@ -6402,7 +6402,7 @@
         <v>0.11543239849718</v>
       </c>
       <c r="Z57" s="149" t="n">
-        <v>0.01391709152328003</v>
+        <v>0.01391709152328001</v>
       </c>
       <c r="AA57" s="149" t="n">
         <v>0</v>
@@ -6414,10 +6414,10 @@
         <v>0</v>
       </c>
       <c r="AD57" s="151" t="n">
-        <v>21.12216940191699</v>
+        <v>21.12216940191698</v>
       </c>
       <c r="AE57" s="152" t="n">
-        <v>2.584078410532202</v>
+        <v>2.5840784105322</v>
       </c>
       <c r="AF57" s="152" t="n">
         <v>0</v>
@@ -6436,10 +6436,10 @@
         </is>
       </c>
       <c r="C58" s="155" t="n">
-        <v>1.983466879944259</v>
+        <v>1.983466879944258</v>
       </c>
       <c r="D58" s="156" t="n">
-        <v>0.3539236137796895</v>
+        <v>0.3539236137796896</v>
       </c>
       <c r="E58" s="156" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
         <v>1.724768611886845</v>
       </c>
       <c r="I58" s="156" t="n">
-        <v>0.2415616461468203</v>
+        <v>0.2415616461468204</v>
       </c>
       <c r="J58" s="156" t="n">
         <v>0</v>
@@ -6466,10 +6466,10 @@
         <v>0</v>
       </c>
       <c r="M58" s="158" t="n">
-        <v>159.0890267589657</v>
+        <v>159.0890267589656</v>
       </c>
       <c r="N58" s="159" t="n">
-        <v>22.97397070598238</v>
+        <v>22.97397070598239</v>
       </c>
       <c r="O58" s="159" t="n">
         <v>0</v>
@@ -6489,7 +6489,7 @@
         <v>1.992416267433915</v>
       </c>
       <c r="U58" s="156" t="n">
-        <v>0.3555205144355466</v>
+        <v>0.3555205144355467</v>
       </c>
       <c r="V58" s="156" t="n">
         <v>0</v>
@@ -6516,10 +6516,10 @@
         <v>0</v>
       </c>
       <c r="AD58" s="158" t="n">
-        <v>159.0890267589657</v>
+        <v>159.0890267589656</v>
       </c>
       <c r="AE58" s="159" t="n">
-        <v>22.97397070598238</v>
+        <v>22.97397070598239</v>
       </c>
       <c r="AF58" s="159" t="n">
         <v>0</v>
@@ -6538,7 +6538,7 @@
         </is>
       </c>
       <c r="C59" s="161" t="n">
-        <v>0.7378225677252895</v>
+        <v>0.7378225677252894</v>
       </c>
       <c r="D59" s="162" t="n">
         <v>0.1299763365534195</v>
@@ -6553,10 +6553,10 @@
         <v>0</v>
       </c>
       <c r="H59" s="161" t="n">
-        <v>0.6735212170763188</v>
+        <v>0.6735212170763187</v>
       </c>
       <c r="I59" s="162" t="n">
-        <v>0.0930616987666837</v>
+        <v>0.09306169876668371</v>
       </c>
       <c r="J59" s="162" t="n">
         <v>0</v>
@@ -6568,7 +6568,7 @@
         <v>0</v>
       </c>
       <c r="M59" s="164" t="n">
-        <v>180.2111961608827</v>
+        <v>180.2111961608826</v>
       </c>
       <c r="N59" s="165" t="n">
         <v>25.55804911651459</v>
@@ -6588,7 +6588,7 @@
         </is>
       </c>
       <c r="T59" s="161" t="n">
-        <v>0.7164251440057219</v>
+        <v>0.7164251440057218</v>
       </c>
       <c r="U59" s="162" t="n">
         <v>0.1262177490316327</v>
@@ -6606,7 +6606,7 @@
         <v>0.6556456752532971</v>
       </c>
       <c r="Z59" s="162" t="n">
-        <v>0.09111893692361447</v>
+        <v>0.09111893692361449</v>
       </c>
       <c r="AA59" s="162" t="n">
         <v>0</v>
@@ -6618,7 +6618,7 @@
         <v>0</v>
       </c>
       <c r="AD59" s="164" t="n">
-        <v>180.2111961608827</v>
+        <v>180.2111961608826</v>
       </c>
       <c r="AE59" s="165" t="n">
         <v>25.55804911651459</v>
@@ -6742,10 +6742,10 @@
         </is>
       </c>
       <c r="C61" s="161" t="n">
-        <v>0.5262909294131163</v>
+        <v>0.5262909294131162</v>
       </c>
       <c r="D61" s="162" t="n">
-        <v>0.08779197128797511</v>
+        <v>0.08779197128797513</v>
       </c>
       <c r="E61" s="162" t="n">
         <v>0</v>
@@ -6757,7 +6757,7 @@
         <v>0</v>
       </c>
       <c r="H61" s="161" t="n">
-        <v>0.4893641086166237</v>
+        <v>0.4893641086166236</v>
       </c>
       <c r="I61" s="162" t="n">
         <v>0.06706268516631567</v>
@@ -6772,7 +6772,7 @@
         <v>0</v>
       </c>
       <c r="M61" s="164" t="n">
-        <v>180.2111961608827</v>
+        <v>180.2111961608826</v>
       </c>
       <c r="N61" s="165" t="n">
         <v>25.55804911651459</v>
@@ -6792,10 +6792,10 @@
         </is>
       </c>
       <c r="T61" s="161" t="n">
-        <v>0.5404028377663317</v>
+        <v>0.5404028377663316</v>
       </c>
       <c r="U61" s="162" t="n">
-        <v>0.09084108234041571</v>
+        <v>0.09084108234041573</v>
       </c>
       <c r="V61" s="162" t="n">
         <v>0</v>
@@ -6807,10 +6807,10 @@
         <v>0</v>
       </c>
       <c r="Y61" s="161" t="n">
-        <v>0.5015422749270683</v>
+        <v>0.5015422749270682</v>
       </c>
       <c r="Z61" s="162" t="n">
-        <v>0.06882741629615188</v>
+        <v>0.0688274162961519</v>
       </c>
       <c r="AA61" s="162" t="n">
         <v>0</v>
@@ -6822,7 +6822,7 @@
         <v>0</v>
       </c>
       <c r="AD61" s="164" t="n">
-        <v>180.2111961608827</v>
+        <v>180.2111961608826</v>
       </c>
       <c r="AE61" s="165" t="n">
         <v>25.55804911651459</v>
@@ -6946,10 +6946,10 @@
         </is>
       </c>
       <c r="C63" s="179" t="n">
-        <v>0.5215240600839796</v>
+        <v>0.5215240600839794</v>
       </c>
       <c r="D63" s="180" t="n">
-        <v>0.08684086405320904</v>
+        <v>0.08684086405320905</v>
       </c>
       <c r="E63" s="180" t="n">
         <v>0</v>
@@ -6961,7 +6961,7 @@
         <v>0</v>
       </c>
       <c r="H63" s="179" t="n">
-        <v>0.4852400788491798</v>
+        <v>0.4852400788491796</v>
       </c>
       <c r="I63" s="180" t="n">
         <v>0.06650627620172743</v>
@@ -6976,7 +6976,7 @@
         <v>0</v>
       </c>
       <c r="M63" s="182" t="n">
-        <v>180.2111961608827</v>
+        <v>180.2111961608826</v>
       </c>
       <c r="N63" s="183" t="n">
         <v>25.55804911651459</v>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="T63" s="185" t="n">
-        <v>0.5265652353520357</v>
+        <v>0.5265652353520356</v>
       </c>
       <c r="U63" s="186" t="n">
-        <v>0.08804721049580098</v>
+        <v>0.088047210495801</v>
       </c>
       <c r="V63" s="186" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="Y63" s="185" t="n">
-        <v>0.4896012633439334</v>
+        <v>0.4896012633439333</v>
       </c>
       <c r="Z63" s="186" t="n">
-        <v>0.06721151898853005</v>
+        <v>0.06721151898853006</v>
       </c>
       <c r="AA63" s="186" t="n">
         <v>0</v>
@@ -7026,7 +7026,7 @@
         <v>0</v>
       </c>
       <c r="AD63" s="188" t="n">
-        <v>180.2111961608827</v>
+        <v>180.2111961608826</v>
       </c>
       <c r="AE63" s="189" t="n">
         <v>25.55804911651459</v>
@@ -7297,49 +7297,49 @@
         </is>
       </c>
       <c r="C68" s="148" t="n">
-        <v>0.7862553395732707</v>
+        <v>0.7862553395732703</v>
       </c>
       <c r="D68" s="149" t="n">
-        <v>0.5386236514696779</v>
+        <v>0.5386236514696777</v>
       </c>
       <c r="E68" s="149" t="n">
-        <v>0.3338437746303801</v>
+        <v>0.33384377463038</v>
       </c>
       <c r="F68" s="149" t="n">
-        <v>0.1632063241579079</v>
+        <v>0.1632063241579078</v>
       </c>
       <c r="G68" s="150" t="n">
-        <v>0.1916738922266969</v>
+        <v>0.1916738922266968</v>
       </c>
       <c r="H68" s="148" t="n">
-        <v>0.7356342151610599</v>
+        <v>0.7356342151610595</v>
       </c>
       <c r="I68" s="149" t="n">
-        <v>0.3951976267794893</v>
+        <v>0.3951976267794891</v>
       </c>
       <c r="J68" s="149" t="n">
-        <v>0.1785994541569898</v>
+        <v>0.1785994541569897</v>
       </c>
       <c r="K68" s="149" t="n">
-        <v>0.07780946864275144</v>
+        <v>0.07780946864275141</v>
       </c>
       <c r="L68" s="150" t="n">
-        <v>0.08207122180880012</v>
+        <v>0.0820712218088001</v>
       </c>
       <c r="M68" s="151" t="n">
-        <v>128.9771540720274</v>
+        <v>128.9771540720273</v>
       </c>
       <c r="N68" s="152" t="n">
-        <v>70.94963046615952</v>
+        <v>70.94963046615949</v>
       </c>
       <c r="O68" s="152" t="n">
-        <v>32.81720286375499</v>
+        <v>32.81720286375497</v>
       </c>
       <c r="P68" s="152" t="n">
         <v>14.67686911281051</v>
       </c>
       <c r="Q68" s="153" t="n">
-        <v>15.97341126043841</v>
+        <v>15.9734112604384</v>
       </c>
       <c r="S68" s="21" t="inlineStr">
         <is>
@@ -7347,49 +7347,49 @@
         </is>
       </c>
       <c r="T68" s="148" t="n">
-        <v>0.7511993690190484</v>
+        <v>0.751199369019048</v>
       </c>
       <c r="U68" s="149" t="n">
-        <v>0.5146085842066986</v>
+        <v>0.5146085842066984</v>
       </c>
       <c r="V68" s="149" t="n">
-        <v>0.3189590203474969</v>
+        <v>0.3189590203474968</v>
       </c>
       <c r="W68" s="149" t="n">
-        <v>0.1559296090680649</v>
+        <v>0.1559296090680648</v>
       </c>
       <c r="X68" s="150" t="n">
         <v>0.183127922509583</v>
       </c>
       <c r="Y68" s="148" t="n">
-        <v>0.7048585759625261</v>
+        <v>0.7048585759625258</v>
       </c>
       <c r="Z68" s="149" t="n">
-        <v>0.3821139856731658</v>
+        <v>0.3821139856731656</v>
       </c>
       <c r="AA68" s="149" t="n">
-        <v>0.1742492020691857</v>
+        <v>0.1742492020691856</v>
       </c>
       <c r="AB68" s="149" t="n">
-        <v>0.07611599601338627</v>
+        <v>0.07611599601338624</v>
       </c>
       <c r="AC68" s="150" t="n">
-        <v>0.08046341748550856</v>
+        <v>0.08046341748550852</v>
       </c>
       <c r="AD68" s="151" t="n">
-        <v>128.9771540720274</v>
+        <v>128.9771540720273</v>
       </c>
       <c r="AE68" s="152" t="n">
-        <v>70.94963046615952</v>
+        <v>70.94963046615949</v>
       </c>
       <c r="AF68" s="152" t="n">
-        <v>32.81720286375499</v>
+        <v>32.81720286375497</v>
       </c>
       <c r="AG68" s="152" t="n">
         <v>14.67686911281051</v>
       </c>
       <c r="AH68" s="153" t="n">
-        <v>15.97341126043841</v>
+        <v>15.9734112604384</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" thickBot="1">
@@ -7411,37 +7411,37 @@
         <v>1.602053914440261</v>
       </c>
       <c r="G69" s="157" t="n">
-        <v>1.710346815181095</v>
+        <v>1.710346815181094</v>
       </c>
       <c r="H69" s="155" t="n">
-        <v>1.35261416558386</v>
+        <v>1.352614165583859</v>
       </c>
       <c r="I69" s="156" t="n">
-        <v>0.7068325252656223</v>
+        <v>0.7068325252656227</v>
       </c>
       <c r="J69" s="156" t="n">
         <v>0.7730950101820778</v>
       </c>
       <c r="K69" s="156" t="n">
-        <v>0.8116847518068822</v>
+        <v>0.811684751806882</v>
       </c>
       <c r="L69" s="157" t="n">
-        <v>0.8557597394813612</v>
+        <v>0.8557597394813611</v>
       </c>
       <c r="M69" s="158" t="n">
         <v>124.7622838797603</v>
       </c>
       <c r="N69" s="159" t="n">
-        <v>67.2240398611049</v>
+        <v>67.22403986110493</v>
       </c>
       <c r="O69" s="159" t="n">
         <v>76.11384329139972</v>
       </c>
       <c r="P69" s="159" t="n">
-        <v>82.87931440324317</v>
+        <v>82.87931440324316</v>
       </c>
       <c r="Q69" s="160" t="n">
-        <v>90.98042324607209</v>
+        <v>90.98042324607208</v>
       </c>
       <c r="S69" s="32" t="inlineStr">
         <is>
@@ -7449,16 +7449,16 @@
         </is>
       </c>
       <c r="T69" s="155" t="n">
-        <v>1.56251131224067</v>
+        <v>1.562511312240669</v>
       </c>
       <c r="U69" s="156" t="n">
-        <v>1.040287094456523</v>
+        <v>1.040287094456524</v>
       </c>
       <c r="V69" s="156" t="n">
         <v>1.459232405884047</v>
       </c>
       <c r="W69" s="156" t="n">
-        <v>1.609282369527976</v>
+        <v>1.609282369527975</v>
       </c>
       <c r="X69" s="157" t="n">
         <v>1.718063887014018</v>
@@ -7467,31 +7467,31 @@
         <v>1.357918033210827</v>
       </c>
       <c r="Z69" s="156" t="n">
-        <v>0.7090061354874583</v>
+        <v>0.7090061354874586</v>
       </c>
       <c r="AA69" s="156" t="n">
         <v>0.7749474709937142</v>
       </c>
       <c r="AB69" s="156" t="n">
-        <v>0.8135361521957306</v>
+        <v>0.8135361521957305</v>
       </c>
       <c r="AC69" s="157" t="n">
-        <v>0.857687308265219</v>
+        <v>0.8576873082652189</v>
       </c>
       <c r="AD69" s="158" t="n">
         <v>124.7622838797603</v>
       </c>
       <c r="AE69" s="159" t="n">
-        <v>67.2240398611049</v>
+        <v>67.22403986110493</v>
       </c>
       <c r="AF69" s="159" t="n">
         <v>76.11384329139972</v>
       </c>
       <c r="AG69" s="159" t="n">
-        <v>82.87931440324317</v>
+        <v>82.87931440324316</v>
       </c>
       <c r="AH69" s="160" t="n">
-        <v>90.98042324607209</v>
+        <v>90.98042324607208</v>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1" thickTop="1">
@@ -7510,13 +7510,13 @@
         <v>0.7228499782918467</v>
       </c>
       <c r="F70" s="162" t="n">
-        <v>0.68865713039355</v>
+        <v>0.6886571303935498</v>
       </c>
       <c r="G70" s="163" t="n">
-        <v>0.7833693494416746</v>
+        <v>0.7833693494416744</v>
       </c>
       <c r="H70" s="161" t="n">
-        <v>0.9483256241026223</v>
+        <v>0.9483256241026219</v>
       </c>
       <c r="I70" s="162" t="n">
         <v>0.5031165104528335</v>
@@ -7525,13 +7525,13 @@
         <v>0.3860052940564485</v>
       </c>
       <c r="K70" s="162" t="n">
-        <v>0.3355519066417119</v>
+        <v>0.3355519066417118</v>
       </c>
       <c r="L70" s="163" t="n">
         <v>0.355394434203442</v>
       </c>
       <c r="M70" s="164" t="n">
-        <v>253.7394379517877</v>
+        <v>253.7394379517876</v>
       </c>
       <c r="N70" s="165" t="n">
         <v>138.1736703272644</v>
@@ -7540,7 +7540,7 @@
         <v>108.9310461551547</v>
       </c>
       <c r="P70" s="165" t="n">
-        <v>97.55618351605369</v>
+        <v>97.55618351605366</v>
       </c>
       <c r="Q70" s="166" t="n">
         <v>106.9538345065105</v>
@@ -7560,13 +7560,13 @@
         <v>0.702560411487803</v>
       </c>
       <c r="W70" s="162" t="n">
-        <v>0.6699102269476597</v>
+        <v>0.6699102269476594</v>
       </c>
       <c r="X70" s="163" t="n">
-        <v>0.7629715589862548</v>
+        <v>0.7629715589862546</v>
       </c>
       <c r="Y70" s="161" t="n">
-        <v>0.9231566555152991</v>
+        <v>0.9231566555152987</v>
       </c>
       <c r="Z70" s="162" t="n">
         <v>0.492613418718215</v>
@@ -7575,13 +7575,13 @@
         <v>0.3801428193678639</v>
       </c>
       <c r="AB70" s="162" t="n">
-        <v>0.3310380525611836</v>
+        <v>0.3310380525611835</v>
       </c>
       <c r="AC70" s="163" t="n">
-        <v>0.3511355713863033</v>
+        <v>0.3511355713863032</v>
       </c>
       <c r="AD70" s="164" t="n">
-        <v>253.7394379517877</v>
+        <v>253.7394379517876</v>
       </c>
       <c r="AE70" s="165" t="n">
         <v>138.1736703272644</v>
@@ -7590,7 +7590,7 @@
         <v>108.9310461551547</v>
       </c>
       <c r="AG70" s="165" t="n">
-        <v>97.55618351605369</v>
+        <v>97.55618351605366</v>
       </c>
       <c r="AH70" s="166" t="n">
         <v>106.9538345065105</v>
@@ -7603,13 +7603,13 @@
         </is>
       </c>
       <c r="C71" s="155" t="n">
-        <v>0.5614499835509486</v>
+        <v>0.5614499835509482</v>
       </c>
       <c r="D71" s="156" t="n">
-        <v>0.7986999651413843</v>
+        <v>0.7986999651413841</v>
       </c>
       <c r="E71" s="156" t="n">
-        <v>1.2708862675694</v>
+        <v>1.270886267569399</v>
       </c>
       <c r="F71" s="156" t="n">
         <v>2.318162421270879</v>
@@ -7618,31 +7618,31 @@
         <v>4.188620606328709</v>
       </c>
       <c r="H71" s="155" t="n">
-        <v>0.5473983630888759</v>
+        <v>0.5473983630888756</v>
       </c>
       <c r="I71" s="156" t="n">
-        <v>0.7087794782764766</v>
+        <v>0.7087794782764765</v>
       </c>
       <c r="J71" s="156" t="n">
-        <v>0.9828904196264997</v>
+        <v>0.9828904196264991</v>
       </c>
       <c r="K71" s="156" t="n">
-        <v>1.618212571974559</v>
+        <v>1.61821257197456</v>
       </c>
       <c r="L71" s="157" t="n">
         <v>2.71569521521337</v>
       </c>
       <c r="M71" s="158" t="n">
-        <v>55.11760726014412</v>
+        <v>55.11760726014408</v>
       </c>
       <c r="N71" s="159" t="n">
-        <v>75.46468991698656</v>
+        <v>75.46468991698654</v>
       </c>
       <c r="O71" s="159" t="n">
-        <v>110.5063472157553</v>
+        <v>110.5063472157552</v>
       </c>
       <c r="P71" s="159" t="n">
-        <v>193.0501805832982</v>
+        <v>193.0501805832983</v>
       </c>
       <c r="Q71" s="160" t="n">
         <v>345.9945070652668</v>
@@ -7653,13 +7653,13 @@
         </is>
       </c>
       <c r="T71" s="155" t="n">
-        <v>0.6727122254722225</v>
+        <v>0.6727122254722221</v>
       </c>
       <c r="U71" s="156" t="n">
-        <v>0.9569779085870976</v>
+        <v>0.9569779085870974</v>
       </c>
       <c r="V71" s="156" t="n">
-        <v>1.522737117154294</v>
+        <v>1.522737117154293</v>
       </c>
       <c r="W71" s="156" t="n">
         <v>2.777551424182554</v>
@@ -7668,31 +7668,31 @@
         <v>5.01867730393566</v>
       </c>
       <c r="Y71" s="155" t="n">
-        <v>0.6526391334870739</v>
+        <v>0.6526391334870735</v>
       </c>
       <c r="Z71" s="156" t="n">
-        <v>0.8307043937027546</v>
+        <v>0.8307043937027544</v>
       </c>
       <c r="AA71" s="156" t="n">
         <v>1.127056309067918</v>
       </c>
       <c r="AB71" s="156" t="n">
-        <v>1.82942793402644</v>
+        <v>1.829427934026441</v>
       </c>
       <c r="AC71" s="157" t="n">
         <v>3.041885776985225</v>
       </c>
       <c r="AD71" s="158" t="n">
-        <v>55.11760726014412</v>
+        <v>55.11760726014408</v>
       </c>
       <c r="AE71" s="159" t="n">
-        <v>75.46468991698656</v>
+        <v>75.46468991698654</v>
       </c>
       <c r="AF71" s="159" t="n">
-        <v>110.5063472157553</v>
+        <v>110.5063472157552</v>
       </c>
       <c r="AG71" s="159" t="n">
-        <v>193.0501805832982</v>
+        <v>193.0501805832983</v>
       </c>
       <c r="AH71" s="160" t="n">
         <v>345.9945070652668</v>
@@ -7705,13 +7705,13 @@
         </is>
       </c>
       <c r="C72" s="161" t="n">
-        <v>0.9019898033153386</v>
+        <v>0.9019898033153383</v>
       </c>
       <c r="D72" s="162" t="n">
         <v>0.7338483740707017</v>
       </c>
       <c r="E72" s="162" t="n">
-        <v>0.9233683693765359</v>
+        <v>0.9233683693765355</v>
       </c>
       <c r="F72" s="162" t="n">
         <v>1.291935715845966</v>
@@ -7720,13 +7720,13 @@
         <v>2.066992709331822</v>
       </c>
       <c r="H72" s="161" t="n">
-        <v>0.8387023439163491</v>
+        <v>0.8387023439163487</v>
       </c>
       <c r="I72" s="162" t="n">
-        <v>0.5605733844235589</v>
+        <v>0.5605733844235588</v>
       </c>
       <c r="J72" s="162" t="n">
-        <v>0.5560573166574118</v>
+        <v>0.5560573166574116</v>
       </c>
       <c r="K72" s="162" t="n">
         <v>0.7087408391149191</v>
@@ -7735,7 +7735,7 @@
         <v>1.057426951683778</v>
       </c>
       <c r="M72" s="164" t="n">
-        <v>308.8570452119318</v>
+        <v>308.8570452119317</v>
       </c>
       <c r="N72" s="165" t="n">
         <v>213.638360244251</v>
@@ -7755,13 +7755,13 @@
         </is>
       </c>
       <c r="T72" s="161" t="n">
-        <v>0.9261756608487663</v>
+        <v>0.926175660848766</v>
       </c>
       <c r="U72" s="162" t="n">
         <v>0.7593357296382719</v>
       </c>
       <c r="V72" s="162" t="n">
-        <v>0.9640535044842722</v>
+        <v>0.9640535044842719</v>
       </c>
       <c r="W72" s="162" t="n">
         <v>1.350843953337567</v>
@@ -7770,13 +7770,13 @@
         <v>2.165952562456961</v>
       </c>
       <c r="Y72" s="161" t="n">
-        <v>0.8595740352589086</v>
+        <v>0.8595740352589083</v>
       </c>
       <c r="Z72" s="162" t="n">
         <v>0.5753246771819167</v>
       </c>
       <c r="AA72" s="162" t="n">
-        <v>0.5705576752696535</v>
+        <v>0.5705576752696533</v>
       </c>
       <c r="AB72" s="162" t="n">
         <v>0.7261116791919525</v>
@@ -7785,7 +7785,7 @@
         <v>1.0827341081461</v>
       </c>
       <c r="AD72" s="164" t="n">
-        <v>308.8570452119318</v>
+        <v>308.8570452119317</v>
       </c>
       <c r="AE72" s="165" t="n">
         <v>213.638360244251</v>
@@ -7909,13 +7909,13 @@
         </is>
       </c>
       <c r="C74" s="179" t="n">
-        <v>0.8938200491198547</v>
+        <v>0.8938200491198544</v>
       </c>
       <c r="D74" s="180" t="n">
         <v>0.7258981197642973</v>
       </c>
       <c r="E74" s="180" t="n">
-        <v>0.9108237625163702</v>
+        <v>0.91082376251637</v>
       </c>
       <c r="F74" s="180" t="n">
         <v>1.273042801833556</v>
@@ -7924,13 +7924,13 @@
         <v>2.035368809510242</v>
       </c>
       <c r="H74" s="179" t="n">
-        <v>0.8316343277471336</v>
+        <v>0.8316343277471332</v>
       </c>
       <c r="I74" s="180" t="n">
-        <v>0.5559223917645369</v>
+        <v>0.5559223917645368</v>
       </c>
       <c r="J74" s="180" t="n">
-        <v>0.5514832802271714</v>
+        <v>0.5514832802271712</v>
       </c>
       <c r="K74" s="180" t="n">
         <v>0.7030172496257847</v>
@@ -7939,7 +7939,7 @@
         <v>1.049088300920424</v>
       </c>
       <c r="M74" s="182" t="n">
-        <v>308.8570452119318</v>
+        <v>308.8570452119317</v>
       </c>
       <c r="N74" s="183" t="n">
         <v>213.638360244251</v>
@@ -7959,13 +7959,13 @@
         </is>
       </c>
       <c r="T74" s="185" t="n">
-        <v>0.9024599257249535</v>
+        <v>0.9024599257249533</v>
       </c>
       <c r="U74" s="186" t="n">
         <v>0.7359819049040363</v>
       </c>
       <c r="V74" s="186" t="n">
-        <v>0.926740103476091</v>
+        <v>0.9267401034760908</v>
       </c>
       <c r="W74" s="186" t="n">
         <v>1.29459528151889</v>
@@ -7974,13 +7974,13 @@
         <v>2.071518399965301</v>
       </c>
       <c r="Y74" s="185" t="n">
-        <v>0.8391087942917715</v>
+        <v>0.8391087942917712</v>
       </c>
       <c r="Z74" s="186" t="n">
         <v>0.5618174783519261</v>
       </c>
       <c r="AA74" s="186" t="n">
-        <v>0.5572783065384872</v>
+        <v>0.5572783065384871</v>
       </c>
       <c r="AB74" s="186" t="n">
         <v>0.709540490026228</v>
@@ -7989,7 +7989,7 @@
         <v>1.058610111841892</v>
       </c>
       <c r="AD74" s="188" t="n">
-        <v>308.8570452119318</v>
+        <v>308.8570452119317</v>
       </c>
       <c r="AE74" s="189" t="n">
         <v>213.638360244251</v>
@@ -8260,22 +8260,22 @@
         </is>
       </c>
       <c r="C79" s="148" t="n">
-        <v>177.8869306673333</v>
+        <v>177.8869306673332</v>
       </c>
       <c r="D79" s="149" t="n">
-        <v>219.3459431118849</v>
+        <v>219.3459431118848</v>
       </c>
       <c r="E79" s="149" t="n">
-        <v>296.072782917626</v>
+        <v>296.0727829176259</v>
       </c>
       <c r="F79" s="149" t="n">
-        <v>295.242830337137</v>
+        <v>295.2428303371369</v>
       </c>
       <c r="G79" s="150" t="n">
-        <v>317.147791703443</v>
+        <v>317.1477917034429</v>
       </c>
       <c r="H79" s="148" t="n">
-        <v>166.4341163010682</v>
+        <v>166.4341163010681</v>
       </c>
       <c r="I79" s="149" t="n">
         <v>160.9379683290898</v>
@@ -8284,13 +8284,13 @@
         <v>158.3927616394047</v>
       </c>
       <c r="K79" s="149" t="n">
-        <v>140.7585635400241</v>
+        <v>140.758563540024</v>
       </c>
       <c r="L79" s="150" t="n">
-        <v>135.796828961347</v>
+        <v>135.7968289613469</v>
       </c>
       <c r="M79" s="151" t="n">
-        <v>29180.53323050612</v>
+        <v>29180.53323050611</v>
       </c>
       <c r="N79" s="152" t="n">
         <v>28893.11222330454</v>
@@ -8299,7 +8299,7 @@
         <v>29104.27366872946</v>
       </c>
       <c r="P79" s="152" t="n">
-        <v>26550.68913359827</v>
+        <v>26550.68913359825</v>
       </c>
       <c r="Q79" s="153" t="n">
         <v>26429.95375305136</v>
@@ -8313,22 +8313,22 @@
         <v>169.9556662426751</v>
       </c>
       <c r="U79" s="149" t="n">
-        <v>209.5661876865142</v>
+        <v>209.5661876865141</v>
       </c>
       <c r="V79" s="149" t="n">
         <v>282.8720855900885</v>
       </c>
       <c r="W79" s="149" t="n">
-        <v>282.0791372647806</v>
+        <v>282.0791372647804</v>
       </c>
       <c r="X79" s="150" t="n">
         <v>303.0074443026525</v>
       </c>
       <c r="Y79" s="148" t="n">
-        <v>159.4712586633399</v>
+        <v>159.4712586633398</v>
       </c>
       <c r="Z79" s="149" t="n">
-        <v>155.6098629071067</v>
+        <v>155.6098629071066</v>
       </c>
       <c r="AA79" s="149" t="n">
         <v>154.5346958616157</v>
@@ -8337,10 +8337,10 @@
         <v>137.6950446796367</v>
       </c>
       <c r="AC79" s="150" t="n">
-        <v>133.136520952262</v>
+        <v>133.1365209522619</v>
       </c>
       <c r="AD79" s="151" t="n">
-        <v>29180.53323050612</v>
+        <v>29180.53323050611</v>
       </c>
       <c r="AE79" s="152" t="n">
         <v>28893.11222330454</v>
@@ -8349,7 +8349,7 @@
         <v>29104.27366872946</v>
       </c>
       <c r="AG79" s="152" t="n">
-        <v>26550.68913359827</v>
+        <v>26550.68913359825</v>
       </c>
       <c r="AH79" s="153" t="n">
         <v>26429.95375305136</v>
@@ -8362,19 +8362,19 @@
         </is>
       </c>
       <c r="C80" s="155" t="n">
-        <v>332.5664272082841</v>
+        <v>332.566427208284</v>
       </c>
       <c r="D80" s="156" t="n">
-        <v>433.1124059806792</v>
+        <v>433.1124059806791</v>
       </c>
       <c r="E80" s="156" t="n">
         <v>582.4222667647952</v>
       </c>
       <c r="F80" s="156" t="n">
-        <v>642.3501252826136</v>
+        <v>642.3501252826135</v>
       </c>
       <c r="G80" s="157" t="n">
-        <v>673.8373513439013</v>
+        <v>673.8373513439011</v>
       </c>
       <c r="H80" s="155" t="n">
         <v>289.1906796206849</v>
@@ -8386,16 +8386,16 @@
         <v>309.9570370624119</v>
       </c>
       <c r="K80" s="156" t="n">
-        <v>325.4483493430395</v>
+        <v>325.4483493430394</v>
       </c>
       <c r="L80" s="157" t="n">
-        <v>337.1496769664295</v>
+        <v>337.1496769664294</v>
       </c>
       <c r="M80" s="158" t="n">
         <v>26674.33964854466</v>
       </c>
       <c r="N80" s="159" t="n">
-        <v>28114.29172847322</v>
+        <v>28114.29172847321</v>
       </c>
       <c r="O80" s="159" t="n">
         <v>30516.32856934188</v>
@@ -8404,7 +8404,7 @@
         <v>33230.802977602</v>
       </c>
       <c r="Q80" s="160" t="n">
-        <v>35844.19655716969</v>
+        <v>35844.19655716968</v>
       </c>
       <c r="S80" s="32" t="inlineStr">
         <is>
@@ -8421,31 +8421,31 @@
         <v>585.0501516065267</v>
       </c>
       <c r="W80" s="156" t="n">
-        <v>645.2484041665771</v>
+        <v>645.248404166577</v>
       </c>
       <c r="X80" s="157" t="n">
-        <v>676.8777003525772</v>
+        <v>676.8777003525771</v>
       </c>
       <c r="Y80" s="155" t="n">
         <v>290.3246534638458</v>
       </c>
       <c r="Z80" s="156" t="n">
-        <v>296.5190037902639</v>
+        <v>296.5190037902638</v>
       </c>
       <c r="AA80" s="156" t="n">
         <v>310.6997443065238</v>
       </c>
       <c r="AB80" s="156" t="n">
-        <v>326.1906759657615</v>
+        <v>326.1906759657614</v>
       </c>
       <c r="AC80" s="157" t="n">
-        <v>337.9090947829326</v>
+        <v>337.9090947829325</v>
       </c>
       <c r="AD80" s="158" t="n">
         <v>26674.33964854466</v>
       </c>
       <c r="AE80" s="159" t="n">
-        <v>28114.29172847322</v>
+        <v>28114.29172847321</v>
       </c>
       <c r="AF80" s="159" t="n">
         <v>30516.32856934188</v>
@@ -8454,7 +8454,7 @@
         <v>33230.802977602</v>
       </c>
       <c r="AH80" s="160" t="n">
-        <v>35844.19655716969</v>
+        <v>35844.19655716968</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" thickTop="1">
@@ -8467,19 +8467,19 @@
         <v>228.6816058354109</v>
       </c>
       <c r="D81" s="162" t="n">
-        <v>289.9131106718629</v>
+        <v>289.9131106718628</v>
       </c>
       <c r="E81" s="162" t="n">
         <v>395.6333162554257</v>
       </c>
       <c r="F81" s="162" t="n">
-        <v>422.0024741042594</v>
+        <v>422.0024741042592</v>
       </c>
       <c r="G81" s="163" t="n">
-        <v>456.1188557721262</v>
+        <v>456.1188557721261</v>
       </c>
       <c r="H81" s="161" t="n">
-        <v>208.7519685933209</v>
+        <v>208.7519685933208</v>
       </c>
       <c r="I81" s="162" t="n">
         <v>207.5747577542209</v>
@@ -8488,25 +8488,25 @@
         <v>211.2700548744362</v>
       </c>
       <c r="K81" s="162" t="n">
-        <v>205.6229850002148</v>
+        <v>205.6229850002147</v>
       </c>
       <c r="L81" s="163" t="n">
-        <v>206.9293402814268</v>
+        <v>206.9293402814267</v>
       </c>
       <c r="M81" s="164" t="n">
-        <v>55854.87287905079</v>
+        <v>55854.87287905077</v>
       </c>
       <c r="N81" s="165" t="n">
-        <v>57007.40395177776</v>
+        <v>57007.40395177775</v>
       </c>
       <c r="O81" s="165" t="n">
-        <v>59620.60223807134</v>
+        <v>59620.60223807133</v>
       </c>
       <c r="P81" s="165" t="n">
-        <v>59781.49211120028</v>
+        <v>59781.49211120025</v>
       </c>
       <c r="Q81" s="166" t="n">
-        <v>62274.15031022105</v>
+        <v>62274.15031022103</v>
       </c>
       <c r="S81" s="42" t="inlineStr">
         <is>
@@ -8514,22 +8514,22 @@
         </is>
       </c>
       <c r="T81" s="161" t="n">
-        <v>222.0496628304454</v>
+        <v>222.0496628304453</v>
       </c>
       <c r="U81" s="162" t="n">
-        <v>281.5295554104341</v>
+        <v>281.529555410434</v>
       </c>
       <c r="V81" s="162" t="n">
         <v>384.5283444893079</v>
       </c>
       <c r="W81" s="162" t="n">
-        <v>410.5145517597419</v>
+        <v>410.5145517597417</v>
       </c>
       <c r="X81" s="163" t="n">
-        <v>444.2421888468288</v>
+        <v>444.2421888468287</v>
       </c>
       <c r="Y81" s="161" t="n">
-        <v>203.2116018600704</v>
+        <v>203.2116018600703</v>
       </c>
       <c r="Z81" s="162" t="n">
         <v>203.2414141306505</v>
@@ -8538,25 +8538,25 @@
         <v>208.0613803608267</v>
       </c>
       <c r="AB81" s="162" t="n">
-        <v>202.8569385808015</v>
+        <v>202.8569385808014</v>
       </c>
       <c r="AC81" s="163" t="n">
         <v>204.4496062499277</v>
       </c>
       <c r="AD81" s="164" t="n">
-        <v>55854.87287905079</v>
+        <v>55854.87287905077</v>
       </c>
       <c r="AE81" s="165" t="n">
-        <v>57007.40395177776</v>
+        <v>57007.40395177775</v>
       </c>
       <c r="AF81" s="165" t="n">
-        <v>59620.60223807134</v>
+        <v>59620.60223807133</v>
       </c>
       <c r="AG81" s="165" t="n">
-        <v>59781.49211120028</v>
+        <v>59781.49211120025</v>
       </c>
       <c r="AH81" s="166" t="n">
-        <v>62274.15031022105</v>
+        <v>62274.15031022103</v>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" thickBot="1">
@@ -8572,10 +8572,10 @@
         <v>781.2995673964291</v>
       </c>
       <c r="E82" s="156" t="n">
-        <v>997.3571793278221</v>
+        <v>997.3571793278225</v>
       </c>
       <c r="F82" s="156" t="n">
-        <v>1178.552133179871</v>
+        <v>1178.55213317987</v>
       </c>
       <c r="G82" s="157" t="n">
         <v>1253.922215918828</v>
@@ -8587,10 +8587,10 @@
         <v>693.3380792859441</v>
       </c>
       <c r="J82" s="156" t="n">
-        <v>771.3458249744554</v>
+        <v>771.3458249744556</v>
       </c>
       <c r="K82" s="156" t="n">
-        <v>822.6981255237297</v>
+        <v>822.6981255237293</v>
       </c>
       <c r="L82" s="157" t="n">
         <v>812.9813802843313</v>
@@ -8602,10 +8602,10 @@
         <v>73820.62371244775</v>
       </c>
       <c r="O82" s="159" t="n">
-        <v>86722.39331668447</v>
+        <v>86722.39331668449</v>
       </c>
       <c r="P82" s="159" t="n">
-        <v>98146.57508444684</v>
+        <v>98146.57508444681</v>
       </c>
       <c r="Q82" s="160" t="n">
         <v>103578.2993426297</v>
@@ -8637,10 +8637,10 @@
         <v>812.6067506706166</v>
       </c>
       <c r="AA82" s="156" t="n">
-        <v>884.4833169103562</v>
+        <v>884.4833169103565</v>
       </c>
       <c r="AB82" s="156" t="n">
-        <v>930.0798660016612</v>
+        <v>930.0798660016609</v>
       </c>
       <c r="AC82" s="157" t="n">
         <v>910.6310913636246</v>
@@ -8652,10 +8652,10 @@
         <v>73820.62371244775</v>
       </c>
       <c r="AF82" s="159" t="n">
-        <v>86722.39331668447</v>
+        <v>86722.39331668449</v>
       </c>
       <c r="AG82" s="159" t="n">
-        <v>98146.57508444684</v>
+        <v>98146.57508444681</v>
       </c>
       <c r="AH82" s="160" t="n">
         <v>103578.2993426297</v>
@@ -8668,7 +8668,7 @@
         </is>
       </c>
       <c r="C83" s="161" t="n">
-        <v>343.1610192308034</v>
+        <v>343.1610192308033</v>
       </c>
       <c r="D83" s="162" t="n">
         <v>449.3946465162136</v>
@@ -8677,28 +8677,28 @@
         <v>615.7951983446501</v>
       </c>
       <c r="F83" s="162" t="n">
-        <v>702.0937451831707</v>
+        <v>702.0937451831704</v>
       </c>
       <c r="G83" s="163" t="n">
-        <v>756.8540886310776</v>
+        <v>756.8540886310774</v>
       </c>
       <c r="H83" s="161" t="n">
-        <v>319.0833755678044</v>
+        <v>319.0833755678042</v>
       </c>
       <c r="I83" s="162" t="n">
-        <v>343.2843715957487</v>
+        <v>343.2843715957486</v>
       </c>
       <c r="J83" s="162" t="n">
-        <v>370.8351259998728</v>
+        <v>370.8351259998729</v>
       </c>
       <c r="K83" s="162" t="n">
-        <v>385.160425549985</v>
+        <v>385.1604255499848</v>
       </c>
       <c r="L83" s="163" t="n">
-        <v>387.189518471633</v>
+        <v>387.1895184716329</v>
       </c>
       <c r="M83" s="164" t="n">
-        <v>117504.3199401748</v>
+        <v>117504.3199401747</v>
       </c>
       <c r="N83" s="165" t="n">
         <v>130828.0276642255</v>
@@ -8707,7 +8707,7 @@
         <v>146342.9955547558</v>
       </c>
       <c r="P83" s="165" t="n">
-        <v>157928.0671956471</v>
+        <v>157928.067195647</v>
       </c>
       <c r="Q83" s="166" t="n">
         <v>165852.4496528507</v>
@@ -8718,22 +8718,22 @@
         </is>
       </c>
       <c r="T83" s="161" t="n">
-        <v>352.3625018768777</v>
+        <v>352.3625018768776</v>
       </c>
       <c r="U83" s="162" t="n">
         <v>465.002613435028</v>
       </c>
       <c r="V83" s="162" t="n">
-        <v>642.9281516428704</v>
+        <v>642.9281516428705</v>
       </c>
       <c r="W83" s="162" t="n">
-        <v>734.1070292617333</v>
+        <v>734.1070292617331</v>
       </c>
       <c r="X83" s="163" t="n">
-        <v>793.089421784383</v>
+        <v>793.0894217843829</v>
       </c>
       <c r="Y83" s="161" t="n">
-        <v>327.0239873661392</v>
+        <v>327.0239873661391</v>
       </c>
       <c r="Z83" s="162" t="n">
         <v>352.3177798978303</v>
@@ -8742,13 +8742,13 @@
         <v>380.505428236588</v>
       </c>
       <c r="AB83" s="162" t="n">
-        <v>394.6004913497576</v>
+        <v>394.6004913497575</v>
       </c>
       <c r="AC83" s="163" t="n">
         <v>396.4560363232254</v>
       </c>
       <c r="AD83" s="164" t="n">
-        <v>117504.3199401748</v>
+        <v>117504.3199401747</v>
       </c>
       <c r="AE83" s="165" t="n">
         <v>130828.0276642255</v>
@@ -8757,7 +8757,7 @@
         <v>146342.9955547558</v>
       </c>
       <c r="AG83" s="165" t="n">
-        <v>157928.0671956471</v>
+        <v>157928.067195647</v>
       </c>
       <c r="AH83" s="166" t="n">
         <v>165852.4496528507</v>
@@ -8872,37 +8872,37 @@
         </is>
       </c>
       <c r="C85" s="179" t="n">
-        <v>340.0528453176586</v>
+        <v>340.0528453176585</v>
       </c>
       <c r="D85" s="180" t="n">
         <v>444.5260635091789</v>
       </c>
       <c r="E85" s="180" t="n">
-        <v>607.4291887153325</v>
+        <v>607.4291887153327</v>
       </c>
       <c r="F85" s="180" t="n">
-        <v>691.8265185760707</v>
+        <v>691.8265185760706</v>
       </c>
       <c r="G85" s="181" t="n">
-        <v>745.2746196903481</v>
+        <v>745.274619690348</v>
       </c>
       <c r="H85" s="179" t="n">
-        <v>316.394356663541</v>
+        <v>316.3943566635408</v>
       </c>
       <c r="I85" s="180" t="n">
-        <v>340.4361930403387</v>
+        <v>340.4361930403386</v>
       </c>
       <c r="J85" s="180" t="n">
         <v>367.7846969791156</v>
       </c>
       <c r="K85" s="180" t="n">
-        <v>382.0499794720344</v>
+        <v>382.0499794720342</v>
       </c>
       <c r="L85" s="181" t="n">
         <v>384.1362218173109</v>
       </c>
       <c r="M85" s="182" t="n">
-        <v>117504.3199401748</v>
+        <v>117504.3199401747</v>
       </c>
       <c r="N85" s="183" t="n">
         <v>130828.0276642255</v>
@@ -8911,7 +8911,7 @@
         <v>146342.9955547558</v>
       </c>
       <c r="P85" s="183" t="n">
-        <v>157928.0671956471</v>
+        <v>157928.067195647</v>
       </c>
       <c r="Q85" s="184" t="n">
         <v>165852.4496528507</v>
@@ -8922,37 +8922,37 @@
         </is>
       </c>
       <c r="T85" s="185" t="n">
-        <v>343.3398767795847</v>
+        <v>343.3398767795846</v>
       </c>
       <c r="U85" s="186" t="n">
         <v>450.7011798118579</v>
       </c>
       <c r="V85" s="186" t="n">
-        <v>618.043810856689</v>
+        <v>618.0438108566891</v>
       </c>
       <c r="W85" s="186" t="n">
-        <v>703.5390681980557</v>
+        <v>703.5390681980555</v>
       </c>
       <c r="X85" s="187" t="n">
-        <v>758.5112243550516</v>
+        <v>758.5112243550515</v>
       </c>
       <c r="Y85" s="185" t="n">
-        <v>319.2380091618695</v>
+        <v>319.2380091618693</v>
       </c>
       <c r="Z85" s="186" t="n">
         <v>344.0462308175253</v>
       </c>
       <c r="AA85" s="186" t="n">
-        <v>371.6494052528012</v>
+        <v>371.6494052528013</v>
       </c>
       <c r="AB85" s="186" t="n">
-        <v>385.5949904406942</v>
+        <v>385.5949904406941</v>
       </c>
       <c r="AC85" s="187" t="n">
-        <v>387.6227467066098</v>
+        <v>387.6227467066097</v>
       </c>
       <c r="AD85" s="188" t="n">
-        <v>117504.3199401748</v>
+        <v>117504.3199401747</v>
       </c>
       <c r="AE85" s="189" t="n">
         <v>130828.0276642255</v>
@@ -8961,7 +8961,7 @@
         <v>146342.9955547558</v>
       </c>
       <c r="AG85" s="189" t="n">
-        <v>157928.0671956471</v>
+        <v>157928.067195647</v>
       </c>
       <c r="AH85" s="190" t="n">
         <v>165852.4496528507</v>
@@ -9762,7 +9762,7 @@
         <v>291.1205744848707</v>
       </c>
       <c r="E94" s="86" t="n">
-        <v>237.6488091302883</v>
+        <v>237.6488091302884</v>
       </c>
       <c r="F94" s="86" t="n">
         <v>224.9387183394504</v>
@@ -9774,7 +9774,7 @@
         <v>25.83840429144</v>
       </c>
       <c r="I94" s="86" t="n">
-        <v>89.98628178148</v>
+        <v>89.98628178147999</v>
       </c>
       <c r="J94" s="86" t="n">
         <v>156.98208016364</v>
@@ -9789,7 +9789,7 @@
         <v>368.2558507821897</v>
       </c>
       <c r="N94" s="86" t="n">
-        <v>381.1068562663506</v>
+        <v>381.1068562663507</v>
       </c>
       <c r="O94" s="86" t="n">
         <v>394.6308892939284</v>
@@ -9824,7 +9824,7 @@
         <v>25.83840429144</v>
       </c>
       <c r="Z94" s="86" t="n">
-        <v>89.98628178148</v>
+        <v>89.98628178147999</v>
       </c>
       <c r="AA94" s="86" t="n">
         <v>156.98208016364</v>
@@ -10006,7 +10006,7 @@
         <v>25.83840429144</v>
       </c>
       <c r="I96" s="133" t="n">
-        <v>89.98628178148</v>
+        <v>89.98628178147999</v>
       </c>
       <c r="J96" s="133" t="n">
         <v>156.98208016364</v>
@@ -10021,10 +10021,10 @@
         <v>371.3856377821897</v>
       </c>
       <c r="N96" s="133" t="n">
-        <v>384.2952962663506</v>
+        <v>384.2952962663507</v>
       </c>
       <c r="O96" s="133" t="n">
-        <v>397.9039822939283</v>
+        <v>397.9039822939284</v>
       </c>
       <c r="P96" s="133" t="n">
         <v>413.3701758442504</v>
@@ -10056,7 +10056,7 @@
         <v>25.83840429144</v>
       </c>
       <c r="Z96" s="136" t="n">
-        <v>89.98628178148</v>
+        <v>89.98628178147999</v>
       </c>
       <c r="AA96" s="136" t="n">
         <v>156.98208016364</v>
